--- a/자료샘플.xlsx
+++ b/자료샘플.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\생산관리\Desktop\시그마자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86A4B95-1AEF-4349-ABC9-5AC465E0E5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4E3437-6F78-49FF-85C5-3CAEBF7FBA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5086B651-7C0A-4EAF-A4FE-248979D703A6}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="255">
   <si>
     <t>거래처명</t>
   </si>
@@ -65,9 +65,6 @@
     <t>해병대교육훈련단</t>
   </si>
   <si>
-    <t>인천시 남동구 청능대로 336 대림시스템 / 오전배송요청 / 도착 전 전화요청</t>
-  </si>
-  <si>
     <t>유진수</t>
   </si>
   <si>
@@ -80,9 +77,6 @@
     <t>경상북도교육청 경상북도영천교육지원청</t>
   </si>
   <si>
-    <t>경북 영천시 금호읍 관정1길 31 거여초등학교</t>
-  </si>
-  <si>
     <t>이례정보기술</t>
   </si>
   <si>
@@ -92,48 +86,12 @@
     <t>A4TC-5NBDN-AH004</t>
   </si>
   <si>
-    <t>경북 영천시 금호읍 금호로 179 금호초등학교</t>
-  </si>
-  <si>
-    <t>경북 영천시 대창면 금창로 787 대창초등학교</t>
-  </si>
-  <si>
-    <t>경북 영천시 호국로 209 영천동부초등학교</t>
-  </si>
-  <si>
-    <t>경북 영천시 조양길 71 영천중앙초등학교</t>
-  </si>
-  <si>
-    <t>경북 영천시 고경면 월천길 1-27 별빛중학교</t>
-  </si>
-  <si>
-    <t>경북 영천시 북안면 운북로 2025 영안중학교</t>
-  </si>
-  <si>
-    <t>경북 영천시 상아탑길 28 영천여자중학교</t>
-  </si>
-  <si>
-    <t>경북 영천시 신녕면 찰방길 8 신녕중학교</t>
-  </si>
-  <si>
-    <t>경북 영천시 신녕면 찰방길 8 경북바이오마이스터고등학교</t>
-  </si>
-  <si>
-    <t>경북 영천시 최무선로 180 영천여자고등학교</t>
-  </si>
-  <si>
-    <t>경북 영천시 남촌길 17 영천성남여자고등학교</t>
-  </si>
-  <si>
     <t>㈜인포셋</t>
   </si>
   <si>
     <t>010-2416-8116</t>
   </si>
   <si>
-    <t>경북 영천시 북안면 신평탑골길 4 경북영광학교</t>
-  </si>
-  <si>
     <t>㈜창조시스템</t>
   </si>
   <si>
@@ -620,9 +578,6 @@
     <t>경기도구리남양주교육청 내양초등학교</t>
   </si>
   <si>
-    <t>경기 구리시 동구릉로 485 내양초등학교 1층 행정실</t>
-  </si>
-  <si>
     <t>이현주</t>
   </si>
   <si>
@@ -686,9 +641,6 @@
     <t>경기도구리남양주교육지원청 갈매유치원</t>
   </si>
   <si>
-    <t>경기 구리시 산마루로 72 갈매유치원 1층 행정실</t>
-  </si>
-  <si>
     <t>이지호</t>
   </si>
   <si>
@@ -779,9 +731,6 @@
     <t>광주광역시 서부교육청 장덕초등학교</t>
   </si>
   <si>
-    <t>광주광역시 광산구 수등로 27-0 장덕초등학교</t>
-  </si>
-  <si>
     <t>A5TQ-5NBDN-AH001</t>
   </si>
   <si>
@@ -801,6 +750,70 @@
   </si>
   <si>
     <t xml:space="preserve">QOT20260800604-1   </t>
+  </si>
+  <si>
+    <t>인천시 남동구 청능대로 336</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>경북 영천시 금호읍 관정1길 31</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>경북 영천시 금호읍 금호로 179</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>경북 영천시 대창면 금창로 787</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>경북 영천시 호국로 209</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>경북 영천시 조양길 71</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">경북 영천시 고경면 월천길 1-27 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>경북 영천시 북안면 운북로 2025</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">경북 영천시 상아탑길 28 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">경북 영천시 신녕면 찰방길 8 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">경북 영천시 최무선로 180 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">경북 영천시 남촌길 17 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">경북 영천시 북안면 신평탑골길 4 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>경기 구리시 동구릉로 485</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>경기 구리시 산마루로 72</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주광역시 광산구 수등로 27-0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -890,13 +903,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1244,24 +1257,24 @@
     <col min="4" max="4" width="12.42578125" customWidth="1"/>
     <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="69.140625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:63" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>0</v>
@@ -1282,192 +1295,192 @@
         <v>5</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Z1" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AP1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AR1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AT1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AU1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AV1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AW1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AX1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AY1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="BA1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="BB1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="BC1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="BD1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="BE1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="BF1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="BG1" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="BH1" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="BI1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AV1" s="3" t="s">
+      <c r="BJ1" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="AW1" s="3" t="s">
+      <c r="BK1" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="AX1" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AY1" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AZ1" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="BA1" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="BB1" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="BC1" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="BD1" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="BE1" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="BF1" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="BG1" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="BH1" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="BI1" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="BJ1" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="BK1" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="K2" s="4">
         <v>47</v>
@@ -1479,61 +1492,61 @@
         <v>7</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="AA2" s="2"/>
       <c r="AB2" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="AG2" s="4">
         <v>1000000</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="AI2" s="4">
         <v>47000000</v>
@@ -1542,101 +1555,101 @@
         <v>47000000</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="AO2" s="2"/>
       <c r="AP2" s="2"/>
       <c r="AQ2" s="2" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AT2" s="2"/>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="BC2" s="2"/>
       <c r="BD2" s="2"/>
       <c r="BE2" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="BG2" s="2"/>
       <c r="BH2" s="2"/>
       <c r="BI2" s="2" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="BJ2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="K3" s="4">
         <v>16</v>
@@ -1645,64 +1658,64 @@
         <v>0</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="O3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P3" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="Q3" s="2" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
       <c r="AA3" s="2"/>
       <c r="AB3" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="AD3" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="AG3" s="4">
         <v>0</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="AI3" s="4">
         <v>0</v>
@@ -1711,97 +1724,97 @@
         <v>0</v>
       </c>
       <c r="AK3" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AL3" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="AN3" s="2" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="AO3" s="2"/>
       <c r="AP3" s="2"/>
       <c r="AQ3" s="2"/>
       <c r="AR3" s="2"/>
       <c r="AS3" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AT3" s="2"/>
       <c r="AU3" s="2"/>
       <c r="AV3" s="2" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="AW3" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AX3" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="AY3" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="AZ3" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="BA3" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="BB3" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="BC3" s="2"/>
       <c r="BD3" s="2"/>
       <c r="BE3" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="BF3" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="BG3" s="2"/>
       <c r="BH3" s="2"/>
       <c r="BI3" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="BJ3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BK3" s="2" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="K4" s="4">
         <v>31</v>
@@ -1810,64 +1823,64 @@
         <v>0</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="O4" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="P4" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="Q4" s="2" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
       <c r="AA4" s="2"/>
       <c r="AB4" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="AD4" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="AE4" s="2" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="AF4" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="AG4" s="4">
         <v>0</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="AI4" s="4">
         <v>0</v>
@@ -1876,97 +1889,97 @@
         <v>0</v>
       </c>
       <c r="AK4" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AL4" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="AM4" s="2" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="AN4" s="2" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="AO4" s="2"/>
       <c r="AP4" s="2"/>
       <c r="AQ4" s="2"/>
       <c r="AR4" s="2"/>
       <c r="AS4" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AT4" s="2"/>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="AW4" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AX4" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="AY4" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="AZ4" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="BA4" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="BB4" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="BC4" s="2"/>
       <c r="BD4" s="2"/>
       <c r="BE4" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="BF4" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="BG4" s="2"/>
       <c r="BH4" s="2"/>
       <c r="BI4" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BJ4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="BK4" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="BJ4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="BK4" s="2" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="K5" s="4">
         <v>10</v>
@@ -1975,64 +1988,64 @@
         <v>0</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="O5" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P5" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="P5" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="Q5" s="2" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
       <c r="AA5" s="2"/>
       <c r="AB5" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="AD5" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="AE5" s="2" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="AG5" s="4">
         <v>0</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="AI5" s="4">
         <v>0</v>
@@ -2041,97 +2054,97 @@
         <v>0</v>
       </c>
       <c r="AK5" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="AN5" s="2" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="AO5" s="2"/>
       <c r="AP5" s="2"/>
       <c r="AQ5" s="2"/>
       <c r="AR5" s="2"/>
       <c r="AS5" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AT5" s="2"/>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="AW5" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AX5" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="AY5" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="AZ5" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="BA5" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="BB5" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="BC5" s="2"/>
       <c r="BD5" s="2"/>
       <c r="BE5" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="BF5" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="BG5" s="2"/>
       <c r="BH5" s="2"/>
       <c r="BI5" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="BJ5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BK5" s="2" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="K6" s="4">
         <v>27</v>
@@ -2140,64 +2153,64 @@
         <v>0</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="O6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P6" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="Q6" s="2" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
       <c r="AA6" s="2"/>
       <c r="AB6" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="AD6" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="AE6" s="2" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="AG6" s="4">
         <v>0</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="AI6" s="4">
         <v>0</v>
@@ -2206,97 +2219,97 @@
         <v>0</v>
       </c>
       <c r="AK6" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AL6" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="AM6" s="2" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="AN6" s="2" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="AO6" s="2"/>
       <c r="AP6" s="2"/>
       <c r="AQ6" s="2"/>
       <c r="AR6" s="2"/>
       <c r="AS6" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AT6" s="2"/>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="AW6" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AX6" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="AY6" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="AZ6" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="BA6" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="BB6" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="BC6" s="2"/>
       <c r="BD6" s="2"/>
       <c r="BE6" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="BF6" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="BG6" s="2"/>
       <c r="BH6" s="2"/>
       <c r="BI6" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="BJ6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BK6" s="2" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="K7" s="4">
         <v>27</v>
@@ -2305,64 +2318,64 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="O7" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P7" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="Q7" s="2" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
       <c r="AA7" s="2"/>
       <c r="AB7" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="AD7" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="AG7" s="4">
         <v>0</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="AI7" s="4">
         <v>0</v>
@@ -2371,97 +2384,97 @@
         <v>0</v>
       </c>
       <c r="AK7" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AL7" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="AM7" s="2" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="AN7" s="2" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="AO7" s="2"/>
       <c r="AP7" s="2"/>
       <c r="AQ7" s="2"/>
       <c r="AR7" s="2"/>
       <c r="AS7" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AT7" s="2"/>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="AW7" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AX7" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="AY7" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="AZ7" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="BA7" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="BB7" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="BC7" s="2"/>
       <c r="BD7" s="2"/>
       <c r="BE7" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="BF7" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="BG7" s="2"/>
       <c r="BH7" s="2"/>
       <c r="BI7" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="BJ7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BK7" s="2" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="K8" s="4">
         <v>24</v>
@@ -2470,64 +2483,64 @@
         <v>0</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="O8" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P8" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="Q8" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
       <c r="AB8" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="AD8" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="AG8" s="4">
         <v>0</v>
       </c>
       <c r="AH8" s="2" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="AI8" s="4">
         <v>0</v>
@@ -2536,97 +2549,97 @@
         <v>0</v>
       </c>
       <c r="AK8" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AL8" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="AM8" s="2" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="AN8" s="2" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="AO8" s="2"/>
       <c r="AP8" s="2"/>
       <c r="AQ8" s="2"/>
       <c r="AR8" s="2"/>
       <c r="AS8" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AT8" s="2"/>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="AW8" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AX8" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="AY8" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="AZ8" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="BA8" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="BB8" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="BC8" s="2"/>
       <c r="BD8" s="2"/>
       <c r="BE8" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="BF8" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="BG8" s="2"/>
       <c r="BH8" s="2"/>
       <c r="BI8" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="BJ8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BK8" s="2" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="I9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="K9" s="4">
         <v>13</v>
@@ -2635,64 +2648,64 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="O9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P9" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="P9" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="Q9" s="2" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
       <c r="AA9" s="2"/>
       <c r="AB9" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="AD9" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="AE9" s="2" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="AG9" s="4">
         <v>0</v>
       </c>
       <c r="AH9" s="2" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="AI9" s="4">
         <v>0</v>
@@ -2701,97 +2714,97 @@
         <v>0</v>
       </c>
       <c r="AK9" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AL9" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="AM9" s="2" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="AN9" s="2" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="AO9" s="2"/>
       <c r="AP9" s="2"/>
       <c r="AQ9" s="2"/>
       <c r="AR9" s="2"/>
       <c r="AS9" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AT9" s="2"/>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="AW9" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AX9" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="AY9" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="AZ9" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="BA9" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="BB9" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="BC9" s="2"/>
       <c r="BD9" s="2"/>
       <c r="BE9" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="BF9" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="BG9" s="2"/>
       <c r="BH9" s="2"/>
       <c r="BI9" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="BJ9" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BK9" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="2" t="s">
+      <c r="I10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="K10" s="4">
         <v>27</v>
@@ -2800,64 +2813,64 @@
         <v>0</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="O10" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P10" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="P10" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="Q10" s="2" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
       <c r="AA10" s="2"/>
       <c r="AB10" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="AC10" s="2" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="AD10" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="AE10" s="2" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="AF10" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="AG10" s="4">
         <v>0</v>
       </c>
       <c r="AH10" s="2" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="AI10" s="4">
         <v>0</v>
@@ -2866,97 +2879,97 @@
         <v>0</v>
       </c>
       <c r="AK10" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AL10" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="AM10" s="2" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="AN10" s="2" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="AO10" s="2"/>
       <c r="AP10" s="2"/>
       <c r="AQ10" s="2"/>
       <c r="AR10" s="2"/>
       <c r="AS10" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AT10" s="2"/>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="AW10" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AX10" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="AY10" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="AZ10" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="BA10" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="BB10" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="BC10" s="2"/>
       <c r="BD10" s="2"/>
       <c r="BE10" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="BF10" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="BG10" s="2"/>
       <c r="BH10" s="2"/>
       <c r="BI10" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="BJ10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BK10" s="2" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="K11" s="4">
         <v>1</v>
@@ -2965,64 +2978,64 @@
         <v>0</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="O11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P11" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="P11" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="Q11" s="2" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
       <c r="AB11" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="AD11" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="AE11" s="2" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="AF11" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="AG11" s="4">
         <v>0</v>
       </c>
       <c r="AH11" s="2" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="AI11" s="4">
         <v>0</v>
@@ -3031,97 +3044,97 @@
         <v>0</v>
       </c>
       <c r="AK11" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AL11" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="AM11" s="2" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="AN11" s="2" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="AO11" s="2"/>
       <c r="AP11" s="2"/>
       <c r="AQ11" s="2"/>
       <c r="AR11" s="2"/>
       <c r="AS11" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AT11" s="2"/>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="AW11" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AX11" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="AY11" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="AZ11" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="BA11" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="BB11" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="BC11" s="2"/>
       <c r="BD11" s="2"/>
       <c r="BE11" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="BF11" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="BG11" s="2"/>
       <c r="BH11" s="2"/>
       <c r="BI11" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="BJ11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BK11" s="2" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="2" t="s">
+      <c r="I12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="K12" s="4">
         <v>9</v>
@@ -3130,64 +3143,64 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="O12" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P12" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="P12" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="Q12" s="2" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
       <c r="AA12" s="2"/>
       <c r="AB12" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="AD12" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="AG12" s="4">
         <v>0</v>
       </c>
       <c r="AH12" s="2" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="AI12" s="4">
         <v>0</v>
@@ -3196,97 +3209,97 @@
         <v>0</v>
       </c>
       <c r="AK12" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AL12" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="AM12" s="2" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="AN12" s="2" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="AO12" s="2"/>
       <c r="AP12" s="2"/>
       <c r="AQ12" s="2"/>
       <c r="AR12" s="2"/>
       <c r="AS12" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AT12" s="2"/>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="AW12" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AX12" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="AY12" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="AZ12" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="BA12" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="BB12" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="BC12" s="2"/>
       <c r="BD12" s="2"/>
       <c r="BE12" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="BF12" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="BG12" s="2"/>
       <c r="BH12" s="2"/>
       <c r="BI12" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="BJ12" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BK12" s="2" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="K13" s="4">
         <v>37</v>
@@ -3295,64 +3308,64 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="O13" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P13" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="P13" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="Q13" s="2" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
       <c r="AA13" s="2"/>
       <c r="AB13" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="AD13" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="AE13" s="2" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="AG13" s="4">
         <v>0</v>
       </c>
       <c r="AH13" s="2" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="AI13" s="4">
         <v>0</v>
@@ -3361,97 +3374,97 @@
         <v>0</v>
       </c>
       <c r="AK13" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AL13" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="AM13" s="2" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="AN13" s="2" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="AO13" s="2"/>
       <c r="AP13" s="2"/>
       <c r="AQ13" s="2"/>
       <c r="AR13" s="2"/>
       <c r="AS13" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AT13" s="2"/>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="AW13" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AX13" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="AY13" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="AZ13" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="BA13" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="BB13" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="BC13" s="2"/>
       <c r="BD13" s="2"/>
       <c r="BE13" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="BF13" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="BG13" s="2"/>
       <c r="BH13" s="2"/>
       <c r="BI13" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="BJ13" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BK13" s="2" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>29</v>
+        <v>250</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K14" s="4">
         <v>20</v>
@@ -3460,64 +3473,64 @@
         <v>0</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="O14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P14" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="Q14" s="2" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
       <c r="AB14" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="AD14" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="AG14" s="4">
         <v>0</v>
       </c>
       <c r="AH14" s="2" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="AI14" s="4">
         <v>0</v>
@@ -3526,97 +3539,97 @@
         <v>0</v>
       </c>
       <c r="AK14" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AL14" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="AM14" s="2" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="AN14" s="2" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="AO14" s="2"/>
       <c r="AP14" s="2"/>
       <c r="AQ14" s="2"/>
       <c r="AR14" s="2"/>
       <c r="AS14" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AT14" s="2"/>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="AW14" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AX14" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="AY14" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="AZ14" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="BA14" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="BB14" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="BC14" s="2"/>
       <c r="BD14" s="2"/>
       <c r="BE14" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="BF14" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="BG14" s="2"/>
       <c r="BH14" s="2"/>
       <c r="BI14" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="BJ14" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BK14" s="2" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>32</v>
+        <v>251</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K15" s="4">
         <v>19</v>
@@ -3625,64 +3638,64 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="O15" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P15" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="P15" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="Q15" s="2" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
       <c r="AA15" s="2"/>
       <c r="AB15" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="AC15" s="2" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="AD15" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="AE15" s="2" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="AG15" s="4">
         <v>0</v>
       </c>
       <c r="AH15" s="2" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="AI15" s="4">
         <v>0</v>
@@ -3691,97 +3704,97 @@
         <v>0</v>
       </c>
       <c r="AK15" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AL15" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="AM15" s="2" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="AN15" s="2" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="AO15" s="2"/>
       <c r="AP15" s="2"/>
       <c r="AQ15" s="2"/>
       <c r="AR15" s="2"/>
       <c r="AS15" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AT15" s="2"/>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="AW15" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AX15" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="AY15" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="AZ15" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="BA15" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="BB15" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="BC15" s="2"/>
       <c r="BD15" s="2"/>
       <c r="BE15" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="BF15" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="BG15" s="2"/>
       <c r="BH15" s="2"/>
       <c r="BI15" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="BJ15" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BK15" s="2" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K16" s="4">
         <v>19</v>
@@ -3793,59 +3806,59 @@
         <v>8</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
       <c r="AA16" s="2"/>
       <c r="AB16" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="AD16" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="AE16" s="2" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="AG16" s="4">
         <v>0</v>
       </c>
       <c r="AH16" s="2" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="AI16" s="4">
         <v>0</v>
@@ -3854,97 +3867,97 @@
         <v>0</v>
       </c>
       <c r="AK16" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AL16" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="AM16" s="2" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="AN16" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="AO16" s="2"/>
       <c r="AP16" s="2"/>
       <c r="AQ16" s="2"/>
       <c r="AR16" s="2"/>
       <c r="AS16" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AT16" s="2"/>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="AW16" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AX16" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="AY16" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="AZ16" s="2" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="BA16" s="2" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="BB16" s="2" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="BC16" s="2"/>
       <c r="BD16" s="2"/>
       <c r="BE16" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="BF16" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="BG16" s="2"/>
       <c r="BH16" s="2"/>
       <c r="BI16" s="2" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="BJ16" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="BK16" s="2" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>195</v>
+        <v>252</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="K17" s="4">
         <v>1</v>
@@ -3953,66 +3966,66 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="V17" s="2" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
       <c r="AA17" s="2" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="AB17" s="2" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="AC17" s="2" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="AD17" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="AE17" s="2" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="AG17" s="4">
         <v>1598182</v>
       </c>
       <c r="AH17" s="2" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="AI17" s="4">
         <v>1598182</v>
@@ -4021,10 +4034,10 @@
         <v>1598182</v>
       </c>
       <c r="AK17" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AL17" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="AM17" s="2"/>
       <c r="AN17" s="2"/>
@@ -4033,81 +4046,81 @@
       <c r="AQ17" s="2"/>
       <c r="AR17" s="2"/>
       <c r="AS17" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AT17" s="2"/>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="AW17" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AX17" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="AY17" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="AZ17" s="2" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="BA17" s="2" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="BB17" s="2" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="BC17" s="2"/>
       <c r="BD17" s="2"/>
       <c r="BE17" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="BF17" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="BG17" s="2"/>
       <c r="BH17" s="2"/>
       <c r="BI17" s="2" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="BJ17" s="2" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="BK17" s="2" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="K18" s="4">
         <v>4</v>
@@ -4116,62 +4129,62 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
       <c r="R18" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
       <c r="AA18" s="2" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="AB18" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="AC18" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="AD18" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE18" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="AC18" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="AD18" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AE18" s="2" t="s">
-        <v>225</v>
-      </c>
       <c r="AF18" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="AG18" s="4">
         <v>1481818.25</v>
       </c>
       <c r="AH18" s="2" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="AI18" s="4">
         <v>5927273</v>
@@ -4180,10 +4193,10 @@
         <v>5927273</v>
       </c>
       <c r="AK18" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AL18" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="AM18" s="2"/>
       <c r="AN18" s="2"/>
@@ -4192,81 +4205,81 @@
       <c r="AQ18" s="2"/>
       <c r="AR18" s="2"/>
       <c r="AS18" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AT18" s="2"/>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="AW18" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AX18" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="AY18" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="AZ18" s="2" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="BA18" s="2" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="BB18" s="2" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="BC18" s="2"/>
       <c r="BD18" s="2"/>
       <c r="BE18" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="BF18" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="BG18" s="2"/>
       <c r="BH18" s="2"/>
       <c r="BI18" s="2" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="BJ18" s="2" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="BK18" s="2" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="K19" s="4">
         <v>32</v>
@@ -4275,66 +4288,66 @@
         <v>0</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="V19" s="2" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="AA19" s="2"/>
       <c r="AB19" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="AC19" s="2" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="AD19" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="AE19" s="2" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="AF19" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="AG19" s="4">
         <v>1</v>
       </c>
       <c r="AH19" s="2" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="AI19" s="4">
         <v>32</v>
@@ -4343,101 +4356,101 @@
         <v>32</v>
       </c>
       <c r="AK19" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AL19" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="AM19" s="2" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="AN19" s="2" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="AO19" s="2"/>
       <c r="AP19" s="2"/>
       <c r="AQ19" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="AR19" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="AS19" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AT19" s="2"/>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="AW19" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AX19" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="AY19" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="AZ19" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="BA19" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="BB19" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="BC19" s="2"/>
       <c r="BD19" s="2"/>
       <c r="BE19" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="BF19" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="BG19" s="2"/>
       <c r="BH19" s="2"/>
       <c r="BI19" s="2" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="BJ19" s="2" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="BK19" s="2" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="I20" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="K20" s="4">
         <v>32</v>
@@ -4446,66 +4459,66 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="Z20" s="2" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="AA20" s="2"/>
       <c r="AB20" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="AC20" s="2" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="AD20" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="AE20" s="2" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="AF20" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="AG20" s="4">
         <v>1</v>
       </c>
       <c r="AH20" s="2" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="AI20" s="4">
         <v>32</v>
@@ -4514,69 +4527,69 @@
         <v>32</v>
       </c>
       <c r="AK20" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AL20" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="AM20" s="2" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="AN20" s="2" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="AO20" s="2"/>
       <c r="AP20" s="2"/>
       <c r="AQ20" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="AR20" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="AS20" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AT20" s="2"/>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="AW20" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AX20" s="2" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="AY20" s="2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="AZ20" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="BA20" s="2" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="BB20" s="2" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="BC20" s="2"/>
       <c r="BD20" s="2"/>
       <c r="BE20" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="BF20" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="BG20" s="2"/>
       <c r="BH20" s="2"/>
       <c r="BI20" s="2" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="BJ20" s="2" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="BK20" s="2" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
